--- a/dev/buildings.xlsx
+++ b/dev/buildings.xlsx
@@ -1816,19 +1816,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/dev/buildings.xlsx
+++ b/dev/buildings.xlsx
@@ -307,7 +307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N134"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.75" customWidth="1" style="5" min="9" max="9"/>
@@ -344,7 +344,7 @@
           <t>Климат</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Рельеф/Геогр. условия</t>
         </is>
@@ -411,16 +411,16 @@
           <t>все (за искл. Арктики)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Степи и Пустыни (если в Пустыни нет Реки/Озера или ресурса "Зерно")</t>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>все (за искл Степи и Пустыни (если в пустыни нет Реки/Озера или ресурса Зерно)</t>
         </is>
       </c>
       <c r="H2" s="9" t="n"/>
       <c r="I2" s="9" t="n"/>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>3 п/п +1(Тёплый/Умеренный) +2(Зерно) +1(Равнина) -1(Холодный/Экватор) -1(Леса) +5(Месопотамия)</t>
+          <t>3 п/п +1(Тёплый/Умеренный) +2(Зерно) +1(Равнина) -1(Холодный/Экватор) -1(Леса) +5(Миср, Саид, Месопотамия)</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
@@ -470,7 +470,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="9" t="n"/>
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="inlineStr">
@@ -516,7 +516,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="9" t="inlineStr">
         <is>
           <t>нет пр-ва при традиции «Вегетарианство»</t>
@@ -653,7 +653,7 @@
           <t>все (за искл. Арктики)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Свобода&gt;0, Поле+Пастбище в локации</t>
@@ -712,7 +712,7 @@
           <t>все (за искл. Арктики)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="inlineStr">
@@ -763,7 +763,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr">
         <is>
           <t>нет пр-ва при Исламе, Иудаизме; традиции "Вегетарианство"; Огород в локации</t>
@@ -818,7 +818,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="9" t="inlineStr">
         <is>
           <t>нет при Исламе/Иудаизме/«Вегетарианство»</t>
@@ -877,7 +877,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -928,7 +928,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Воск</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -936,25 +936,21 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>1 Инструмент</t>
-        </is>
-      </c>
+      <c r="I12" s="9" t="n"/>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>1 п/п</t>
+          <t>1 п/п + 1 (Леса), 1 Сахар, 1 Алко</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>+1 Фрукты/Овощи, наличие Ирригации даёт х2, «Удобрения», «Мелиорация», «Кяризы», «Феллахи»</t>
+          <t>«Пчеловодство», «Мёдоварение»</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -992,10 +988,10 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Тёплый/Жаркий/Знойный/Экватор (кроме Холодного/Прохладного/Степи/Пустыни/Холмов)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>все (за искл. Холодного, Прохладного и Арктики)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1054,7 +1050,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1113,7 +1109,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1172,7 +1168,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="9" t="inlineStr">
         <is>
           <t>не больше чем Шор/артелей</t>
@@ -1276,7 +1272,7 @@
           <t>Тёплый/Жаркий/Знойный/Экватор</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Степь/Пустыня/Холмы</t>
         </is>
@@ -1322,7 +1318,7 @@
           <t>Жаркий/Знойный/Экватор</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Холмы/Пустыня/Джунгли(x3)</t>
         </is>
@@ -1372,7 +1368,7 @@
           <t>Экватор/Жаркий/Знойный</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Равнина/Джунгли/Болото(50%)</t>
         </is>
@@ -1418,7 +1414,7 @@
           <t>Жаркий/Знойный/Экватор</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Джунгли/Холмы/Болото</t>
         </is>
@@ -1468,7 +1464,7 @@
           <t>Жаркий/Знойный</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Пустыня/Равнина</t>
         </is>
@@ -1552,7 +1548,7 @@
           <t>Жаркий</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Леса</t>
         </is>
@@ -1602,7 +1598,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
           <t>инн «Пенька»</t>
@@ -1644,7 +1640,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr">
         <is>
           <t>Язычество</t>
@@ -1699,7 +1695,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr">
         <is>
           <t>ранг страны &gt;=3, 1 на страну</t>
@@ -1754,7 +1750,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="9" t="inlineStr">
         <is>
           <t>1 на страну</t>
@@ -1809,7 +1805,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
           <t>ранг страны &gt;=2, 1 на страну</t>
@@ -1864,7 +1860,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1919,7 +1915,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1974,7 +1970,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2015,7 +2011,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Рудник</t>
+          <t>Золото</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -2023,35 +2019,34 @@
           <t>Провинция</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n"/>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Золото</t>
+        </is>
+      </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
           <t>все с соотв. ресурсом, в т.ч. Болото (Ж/руда)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="9" t="n"/>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>1 Рабы/1 Инструмент</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="n"/>
+          <t>1 Инструмент</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>2 Золото</t>
+        </is>
+      </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
           <t>«Маркшейдеры», «Амальгамация», «Горное дело», «Тяга», «Водяные насосы»</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>1+1(Дорога)</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="L33" s="9" t="n"/>
     </row>
     <row r="34" ht="12.75" customHeight="1" s="6">
       <c r="A34" s="5" t="inlineStr">
@@ -2066,7 +2061,7 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Золото</t>
+          <t>Серебро</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
@@ -2076,7 +2071,7 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Золото</t>
+          <t>Серебро</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
@@ -2084,16 +2079,12 @@
           <t>все с соотв. ресурсом, в т.ч. Болото (Ж/руда)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>1 Инструмент</t>
-        </is>
-      </c>
+      <c r="I34" s="9" t="n"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>2 Золото</t>
+          <t>2 Серебро</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
@@ -2116,7 +2107,7 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Серебро</t>
+          <t>Железо</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -2126,7 +2117,7 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Серебро</t>
+          <t>Железо</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
@@ -2134,12 +2125,12 @@
           <t>все с соотв. ресурсом, в т.ч. Болото (Ж/руда)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="9" t="n"/>
       <c r="I35" s="9" t="n"/>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>2 Серебро</t>
+          <t>4 Жел/руда +1(Железо) -2(Болото)</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr">
@@ -2162,7 +2153,7 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Железо</t>
+          <t>Медь</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -2172,7 +2163,7 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Железо</t>
+          <t>Медь</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
@@ -2180,12 +2171,12 @@
           <t>все с соотв. ресурсом, в т.ч. Болото (Ж/руда)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>4 Жел/руда +1(Железо) -2(Болото)</t>
+          <t>3 Мед/руда</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -2208,7 +2199,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Медь</t>
+          <t>Др/камни</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -2218,7 +2209,7 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Медь</t>
+          <t>Др/камни</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
@@ -2226,12 +2217,12 @@
           <t>все с соотв. ресурсом, в т.ч. Болото (Ж/руда)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="9" t="n"/>
       <c r="I37" s="9" t="n"/>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>3 Мед/руда</t>
+          <t>1 Др/камни</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">
@@ -2254,7 +2245,7 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Др/камни</t>
+          <t>Свинец</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
@@ -2264,7 +2255,7 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Др/камни</t>
+          <t>Свинец</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
@@ -2272,12 +2263,12 @@
           <t>все с соотв. ресурсом, в т.ч. Болото (Ж/руда)</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>1 Др/камни</t>
+          <t>2 Свинец</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
@@ -2290,7 +2281,7 @@
     <row r="39" ht="35.25" customHeight="1" s="6">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Рудник</t>
+          <t>Шахта</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -2300,7 +2291,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Свинец</t>
+          <t>Шахта</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -2308,30 +2299,26 @@
           <t>Провинция</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>Свинец</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>все с соотв. ресурсом, в т.ч. Болото (Ж/руда)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
       <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>2 Свинец</t>
-        </is>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
-        <is>
-          <t>«Маркшейдеры», «Амальгамация», «Горное дело», «Тяга», «Водяные насосы»</t>
-        </is>
-      </c>
-      <c r="L39" s="9" t="n"/>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>1 Рабы/1 Инструмент</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>1+1(Дорога)</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="35.25" customHeight="1" s="6">
       <c r="A40" s="5" t="inlineStr">
@@ -2346,7 +2333,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Шахта</t>
+          <t>Соль</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -2354,26 +2341,26 @@
           <t>Провинция</t>
         </is>
       </c>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Соль</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>1 Рабы/1 Инструмент</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="n"/>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>3 Соль</t>
+        </is>
+      </c>
       <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="inlineStr">
-        <is>
-          <t>1+1(Дорога)</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="L40" s="9" t="n"/>
     </row>
     <row r="41" ht="46.5" customHeight="1" s="6">
       <c r="A41" s="5" t="inlineStr">
@@ -2388,7 +2375,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Соль</t>
+          <t>Селитра</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2398,7 +2385,7 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Соль</t>
+          <t>Селитра</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -2406,12 +2393,12 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="9" t="n"/>
       <c r="I41" s="9" t="n"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>3 Соль</t>
+          <t>3 Селитра</t>
         </is>
       </c>
       <c r="K41" s="9" t="n"/>
@@ -2430,7 +2417,7 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Селитра</t>
+          <t>Уголь</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -2440,7 +2427,7 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Селитра</t>
+          <t>Уголь</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
@@ -2448,23 +2435,19 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>3 Селитра</t>
+          <t>4,5 Уголь</t>
         </is>
       </c>
       <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n"/>
     </row>
     <row r="43" ht="12.75" customHeight="1" s="6">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Шахта</t>
-        </is>
-      </c>
+      <c r="A43" s="5" t="n"/>
       <c r="B43" s="9" t="inlineStr">
         <is>
           <t>добыча</t>
@@ -2472,7 +2455,7 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Уголь</t>
+          <t>Лесорубка</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2482,7 +2465,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Уголь</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
@@ -2490,16 +2473,33 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" s="9" t="n"/>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="I43" s="9" t="n"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>4,5 Уголь</t>
-        </is>
-      </c>
-      <c r="K43" s="9" t="n"/>
-      <c r="L43" s="9" t="n"/>
+          <t>6 древесина, -2 Джунгли, -4 иной ландшафт</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>«Пила»</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>0+2 (тех. Водяное колесо + Река)</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="46.5" customHeight="1" s="6">
       <c r="A44" s="5" t="n"/>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Лесорубка</t>
+          <t>Углежогня</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -2525,10 +2525,10 @@
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>все</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>Леса/Джунгли</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2536,27 +2536,27 @@
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>3 Древесина</t>
+          <t>1 Древесина</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>6 древесина</t>
+          <t>2 Уголь</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>-2 Джунгли, -4 иной ландшафт, «Пила»</t>
+          <t>-1 Джунгли, «Угольная печь», «Чугун»</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>0+2 (тех. Водяное колесо + Река)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Углежогня</t>
+          <t>Смолокурня</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2587,7 +2587,7 @@
           <t>Леса/Джунгли</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2595,27 +2595,27 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>1 Древесина</t>
+          <t>1 Рабы</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>2 Уголь</t>
+          <t>1 Смола</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>-1 Джунгли, «Угольная печь», «Чугун»</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Смолокурня</t>
+          <t>Каменоломня</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -2643,10 +2643,10 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>Леса/Джунгли</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>все</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2654,27 +2654,27 @@
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>1 Рабы</t>
+          <t>1 Инструмент</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>1 Смола</t>
+          <t>4 Камень</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1 Пустыня, -2 иной ландшафт, «Горное дело»</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,5+1 (Мрамор)</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Каменоломня</t>
+          <t>Солеварня</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Соль</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
@@ -2705,7 +2705,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2713,27 +2713,27 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>1 Инструмент</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>4 Камень</t>
+          <t>3 Соль</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>-1 Пустыня, -2 иной ландшафт, «Горное дело»</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>1,5+1 (Мрамор)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Солеварня</t>
+          <t>Селитряница</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Соль</t>
+          <t>Селитра</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -2764,7 +2764,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2777,22 +2777,22 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>3 Соль</t>
+          <t>3 Селитра</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Маркшейдеры», «Штольня», «Горное дело», «Чугун», «Водяные насосы», «Копи»</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Селитряница</t>
+          <t>Бивак</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Селитра</t>
+          <t>Море</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
@@ -2823,25 +2823,25 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>нужна Скот/Свинарник/Канализация</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 Звери + !ТНП (Слоны)</t>
         </is>
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>3 Селитра</t>
+          <t>1 Соль + 1 Селитра</t>
         </is>
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>«Маркшейдеры», «Штольня», «Горное дело», «Чугун», «Водяные насосы», «Копи»</t>
+          <t>«Порох»</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2864,17 +2864,17 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Бивак</t>
+          <t>Угодье</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Провинция</t>
+          <t>Провинция/Город</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Море</t>
+          <t>Скот/Свинарник/Канализация</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
@@ -2882,35 +2882,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>нужна Скот/Свинарник/Канализация</t>
+          <t>нет при «Вегетарианство»</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>1 Звери + !ТНП (Слоны)</t>
+          <t>1 Кони, 1 Волокно</t>
         </is>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>1 Соль + 1 Селитра</t>
+          <t>1 Звери + 1 ТНП (Слоны)</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>«Порох»</t>
+          <t>«Травля зверей»</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
     </row>
@@ -2918,58 +2918,58 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>добыча</t>
+          <t>ремесло</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Угодье</t>
+          <t>Гончарная</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Провинция/Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Скот/Свинарник/Канализация</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>все</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Река/Озеро</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>нет при «Вегетарианство»</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>1 Кони, 1 Волокно</t>
+          <t>1 Древесина</t>
         </is>
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>1 Звери + 1 ТНП (Слоны)</t>
+          <t>2 ТНП, 2 Камень</t>
         </is>
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>«Травля зверей»</t>
+          <t>«Кирпич», «Глазурь», «Фаянс»</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>12.5</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Гончарная</t>
+          <t>Красильня</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -2997,10 +2997,10 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>Река/Озеро</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>все</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -3008,27 +3008,27 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>1 Древесина</t>
+          <t>1 Древесина, 1 Сахар</t>
         </is>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>2 ТНП</t>
+          <t>0 Краски +2 (Краситель)</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>«Кирпич», «Глазурь», «Фаянс»</t>
+          <t>«Шафран», «Киноварь», «Охра»</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Красильня</t>
+          <t>Пекарня</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -3059,30 +3059,30 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>не больше 2 на 1 Мельницу</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>1 Древесина, 1 Сахар</t>
+          <t>1 древесина, 1 сахар</t>
         </is>
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>0 Краски +2 (Краситель)</t>
-        </is>
-      </c>
-      <c r="K53" s="9" t="inlineStr">
-        <is>
-          <t>«Шафран», «Киноварь», «Охра»</t>
-        </is>
-      </c>
+          <t>3 п/п + 2 (Сахар*)</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1+2(Сахар)</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
@@ -3100,17 +3100,17 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Пекарня</t>
+          <t>Пивоварня</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Зерно/Овощи/Фрукты</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
@@ -3118,30 +3118,26 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>не больше 2 на 1 Мельницу</t>
-        </is>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>2 Сахар + Стекло</t>
-        </is>
-      </c>
+          <t>нет пр-ва при Исламе, не больше чем провинций с Зерном и Рисом</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="n"/>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>3 п/п</t>
+          <t>2 Алко</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>+2 (Сахар)</t>
+          <t>+1 (инн Эль + Леса) «Хмель»</t>
         </is>
       </c>
       <c r="L54" s="9" t="inlineStr">
         <is>
-          <t>1+2(Сахар)</t>
+          <t>2+1 (Боч/артель +1 инн Эль + Леса)</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
@@ -3159,17 +3155,17 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Пивоварня</t>
+          <t>Винокурня</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Провинция</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Зерно/Овощи/Фрукты</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
@@ -3177,35 +3173,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>нет при Исламе</t>
+          <t>нет при Исламе, не больше чем провинций с Зерном и Рисом</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>4 Волокно</t>
+          <t>1 Кожа</t>
         </is>
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>2 Алко</t>
+          <t>5 Алко</t>
         </is>
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>+1 (инн Эль + Леса) «Хмель»</t>
+          <t>«Водка», «Ракия»</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
         <is>
-          <t>2+1 (Боч/артель +1 инн Эль + Леса)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3214,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Винокурня</t>
+          <t>Свеч/артель</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -3228,7 +3224,7 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Воск</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -3236,35 +3232,31 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>нет при Исламе, не больше чем провинций с Зерном и Рисом</t>
-        </is>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>1 Кожа</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="n"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>5 Алко</t>
+          <t>1 Благовония</t>
         </is>
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>«Водка», «Ракия»</t>
+          <t>«Гильдии»</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -3277,17 +3269,17 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Свечной двор</t>
+          <t>Бумажная артель</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Воск</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
@@ -3295,7 +3287,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -3303,27 +3295,27 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>1 Соль</t>
+          <t>1 Волокно, Смола</t>
         </is>
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>1 Благовония</t>
+          <t>3 Бумага</t>
         </is>
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>«Гильдии»</t>
+          <t>«Гербовая бумага», «Водяное колесо», «Механизация труда», «Гильдии»</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3328,7 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Бумажная артель</t>
+          <t>Пергаментная артель</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -3354,7 +3346,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -3362,27 +3354,27 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>1 Волокно, Смола</t>
+          <t>2 Волокно</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>3 Бумага</t>
+          <t>1 Бумага</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>«Гербовая бумага», «Водяное колесо», «Механизация труда», «Гильдии»</t>
+          <t>«Золение», «Велен»</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -3395,17 +3387,17 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Пергаментная артель</t>
+          <t>Дубильня</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Провинция/Город</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Скот/Меха/Звери/Свинарник</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
@@ -3413,7 +3405,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -3421,22 +3413,22 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>2 Волокно</t>
+          <t>3 Волокно + 1 Краски</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>1 Бумага</t>
+          <t>3 Кожа</t>
         </is>
       </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>«Золение», «Велен»</t>
+          <t>«Сафьян», «Юфть», «Замша»</t>
         </is>
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
@@ -3454,17 +3446,17 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Дубильня</t>
+          <t>Верфь</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Провинция/Город</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Скот/Меха/Звери/Свинарник</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
@@ -3472,35 +3464,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>не больше чем провинций с Овцами</t>
         </is>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>3 Волокно + 1 Краски</t>
+          <t>2 Волокно</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>3 Кожа</t>
+          <t>1 КОР + 1 (Смола) +1 (Пуш/двор)</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>«Сафьян», «Юфть», «Замша»</t>
+          <t>«Сухой док», «Клинкер», «Адмиралтейство», «Ветряная пилорама»</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -3513,12 +3505,12 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Верфь</t>
+          <t>Ткацкая артель</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -3531,25 +3523,25 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>не больше чем провинций с Овцами</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>2 Волокно</t>
+          <t>3 Волокно + 1 Краски</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>1 КОР + 1 (Смола) +1 (Пуш/двор)</t>
+          <t>1 Ткани</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>«Сухой док», «Клинкер», «Адмиралтейство», «Ветряная пилорама»</t>
+          <t>«Ткацкий станок», «Гильдии», «Муслин», «Тартан», «Вадмаль», «Свитер»</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
@@ -3559,7 +3551,7 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12.5</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3564,12 @@
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Ткацкая артель</t>
+          <t>Мануфактура</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3590,7 +3582,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -3598,27 +3590,27 @@
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>3 Волокно + 1 Краски</t>
+          <t>2 Волокно</t>
         </is>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>1 Ткани</t>
+          <t>6 Ткани</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>«Ткацкий станок», «Гильдии», «Муслин», «Тартан», «Вадмаль», «Свитер»</t>
+          <t>«Экономика», «Разделение труда», «Цеховые привилегии»</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3623,12 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Мануфактура</t>
+          <t>Сукновальня</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3649,7 +3641,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -3657,17 +3649,17 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>2 Волокно</t>
+          <t>Соль + 1 Древесина</t>
         </is>
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>6 Ткани</t>
+          <t>2 ТНП</t>
         </is>
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
-          <t>«Экономика», «Разделение труда», «Цеховые привилегии»</t>
+          <t>«Валенки», «Водяное колесо», «Войлок»</t>
         </is>
       </c>
       <c r="L63" s="9" t="inlineStr">
@@ -3690,12 +3682,12 @@
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Сукновальня</t>
+          <t>Ковровый двор</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3708,35 +3700,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>нет при «Вегетарианство», не больше чем Свинарников</t>
         </is>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>Соль + 1 Древесина</t>
+          <t>1 Соль + 1 Пряности</t>
         </is>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>2 ТНП</t>
+          <t>1 Украшения</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>«Валенки», «Водяное колесо», «Войлок»</t>
+          <t>«Арабеска»</t>
         </is>
       </c>
       <c r="L64" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3741,7 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Ковровый двор</t>
+          <t>Коптильня</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3767,25 +3759,25 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>нет при «Вегетарианство», не больше чем Свинарников</t>
+          <t>не больше чем локаций с Рыбой</t>
         </is>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>1 Соль + 1 Пряности</t>
+          <t>1 Соль</t>
         </is>
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>1 Украшения</t>
+          <t>4 п/п</t>
         </is>
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>«Арабеска»</t>
+          <t>+1 (Боч/артель)</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr">
@@ -3795,7 +3787,7 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3800,12 @@
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Коптильня</t>
+          <t>Колбасный цех</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Провинция/Город</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3826,35 +3818,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>не больше чем локаций с Рыбой</t>
+          <t>нет при «Вегетарианство»</t>
         </is>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>1 Соль</t>
+          <t>1 Золото/Серебро/Др.камни</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>4 п/п</t>
+          <t>7 п/п</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
         <is>
-          <t>+1 (Боч/артель)</t>
+          <t>«Кровяная колбаса»</t>
         </is>
       </c>
       <c r="L66" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -3867,12 +3859,12 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Колбасный цех</t>
+          <t>Сыроварня</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Провинция/Город</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3885,35 +3877,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>нет при «Вегетарианство»</t>
+          <t>не больше чем локаций с Овцами и Скотом</t>
         </is>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>1 Золото/Серебро/Др.камни</t>
+          <t>1 Древесина + 1 Кожа</t>
         </is>
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>7 п/п</t>
+          <t>3 п/п</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr">
         <is>
-          <t>«Кровяная колбаса»</t>
+          <t>«Элитное сыроварение»</t>
         </is>
       </c>
       <c r="L67" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17.5</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3918,7 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Сыроварня</t>
+          <t>Ювелирная артель</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3944,35 +3936,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>не больше чем локаций с Овцами и Скотом</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>1 Древесина + 1 Кожа</t>
+          <t>1 Соль + 1 Уголь</t>
         </is>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>3 п/п</t>
+          <t>1 Украшения (Серебро) + 1 (Золото) + 2 (Др/камни)</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
-          <t>«Элитное сыроварение»</t>
+          <t>«Бусы», «Гильдии», «Огранка»</t>
         </is>
       </c>
       <c r="L68" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+1 (Евреи)</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3977,7 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Ювелирная артель</t>
+          <t>Шорная артель</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -4003,33 +3995,33 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>работает в Пустыне или Городе</t>
         </is>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>1 Соль + 1 Уголь</t>
+          <t>1 Благовония</t>
         </is>
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>1 Украшения (Серебро) + 1 (Золото) + 2 (Др/камни)</t>
+          <t>2 ТНП</t>
         </is>
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>«Бусы», «Гильдии», «Огранка»</t>
+          <t>«Гильдии», «Дилижансы», «Производство сбруи», «Коя»</t>
         </is>
       </c>
       <c r="L69" s="9" t="inlineStr">
         <is>
-          <t>4+1 (Евреи)</t>
-        </is>
-      </c>
-      <c r="M69" s="5" t="inlineStr">
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -4044,7 +4036,7 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Шорная артель</t>
+          <t>Стеклянная артель</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -4062,35 +4054,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>работает в Пустыне или Городе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>1 Благовония</t>
+          <t>1 Кожа</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>2 ТНП</t>
+          <t>2 Стекло</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
-          <t>«Гильдии», «Дилижансы», «Производство сбруи», «Коя»</t>
+          <t>«Хрусталь», «Гильдии», «Оптика»</t>
         </is>
       </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M70" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4095,7 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Стеклянная артель</t>
+          <t>Мыловарня</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -4121,7 +4113,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -4129,27 +4121,27 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>1 Кожа</t>
+          <t>2 Ткани + 1 Кожа</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>2 Стекло</t>
+          <t>3 ТНП</t>
         </is>
       </c>
       <c r="K71" s="9" t="inlineStr">
         <is>
-          <t>«Хрусталь», «Гильдии», «Оптика»</t>
+          <t>«Твёрдое мыло», «Гигиена»</t>
         </is>
       </c>
       <c r="L71" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="M71" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4154,7 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Мыловарня</t>
+          <t>Обувная артель</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -4180,7 +4172,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -4188,27 +4180,27 @@
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>2 Ткани + 1 Кожа</t>
+          <t>1 Древесина</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>3 ТНП</t>
+          <t>2 ТНП</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
         <is>
-          <t>«Твёрдое мыло», «Гигиена»</t>
+          <t>«Гильдии», «Пулены», «Бабуши», «Башмаки»</t>
         </is>
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M72" s="9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4213,7 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Обувная артель</t>
+          <t>Швейная артель</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -4239,7 +4231,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -4247,27 +4239,27 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>1 Древесина</t>
+          <t>3 Медь + 2 Уголь</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>2 ТНП</t>
+          <t>4 ТНП</t>
         </is>
       </c>
       <c r="K73" s="9" t="inlineStr">
         <is>
-          <t>«Гильдии», «Пулены», «Бабуши», «Башмаки»</t>
+          <t>«Сапоги», «Гильдии», «Кафтан», «Феска», «Шешия», «Пуговица», «Бернус», «Кулах», «Сарафан», «Шаровары», «Ферязь», «Дублет», «Дивитисий», «Тюбетейка», «Свитер»</t>
         </is>
       </c>
       <c r="L73" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M73" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -4280,12 +4272,12 @@
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Швейная артель</t>
+          <t>Бондарная артель</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Провинция</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -4298,7 +4290,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -4306,27 +4298,27 @@
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>3 Медь + 2 Уголь</t>
+          <t>2 Селитра + 1 Уголь</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>4 ТНП</t>
+          <t>1 ТНП</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
-          <t>«Сапоги», «Гильдии», «Кафтан», «Феска», «Шешия», «Пуговица», «Бернус», «Кулах», «Сарафан», «Шаровары», «Ферязь», «Дублет», «Дивитисий», «Тюбетейка», «Свитер»</t>
+          <t>«Гильдии», «Бордоские бочки»</t>
         </is>
       </c>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M74" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -4339,17 +4331,17 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Бондарная артель</t>
+          <t>Пушной двор</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Провинция</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Пустыня</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
@@ -4357,7 +4349,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -4365,27 +4357,27 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>2 Селитра + 1 Уголь</t>
+          <t>1 Древесина + 1 Железо</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>1 ТНП</t>
+          <t>2 Пуш</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>«Гильдии», «Бордоские бочки»</t>
+          <t>«Топчу», «Эргастерии», «Серпантина»</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -4398,17 +4390,17 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Пушной двор</t>
+          <t>Пороховая артель</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>Пустыня</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
@@ -4416,7 +4408,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -4429,22 +4421,22 @@
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>2 Пуш</t>
+          <t>4 Порох</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>«Топчу», «Эргастерии», «Серпантина»</t>
+          <t>«Химия», «Баллистика», «Гильдии», «Зернистый порох», «Эргастерии»</t>
         </is>
       </c>
       <c r="L76" s="9" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M76" s="9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4449,7 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Пороховая артель</t>
+          <t>Мастерская</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -4475,7 +4467,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -4483,17 +4475,17 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>1 Древесина + 1 Железо</t>
+          <t>1 Медь</t>
         </is>
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>4 Порох</t>
+          <t>3 Инструмент</t>
         </is>
       </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>«Химия», «Баллистика», «Гильдии», «Зернистый порох», «Эргастерии»</t>
+          <t>«Токарный станок», «Механизация труда»</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr">
@@ -4503,7 +4495,7 @@
       </c>
       <c r="M77" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27.5</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4508,12 @@
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Мастерская</t>
+          <t>Кузница</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Провинция</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -4534,7 +4526,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -4542,27 +4534,27 @@
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>1 Медь</t>
+          <t>1 Медь + 1 Инструмент</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>3 Инструмент</t>
+          <t>2 Х/о</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>«Токарный станок», «Механизация труда»</t>
+          <t>«Горн», «Вагранка», «Сыродутная печь», «Булатная сталь», «Подкова»</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M78" s="9" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -4575,12 +4567,12 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Кузница</t>
+          <t>Плавильня</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Провинция</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -4593,35 +4585,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 Ж/руда + 2 Уголь</t>
         </is>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>1 Медь + 1 Инструмент</t>
+          <t>2 Свинец + 1 Инструмент</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>2 Х/о</t>
+          <t>4 Железо</t>
         </is>
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>«Горн», «Вагранка», «Сыродутная печь», «Булатная сталь», «Подкова»</t>
+          <t>«Чугун», «Доменная печь», «Тигельная сталь»</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+2(Железо)</t>
         </is>
       </c>
       <c r="M79" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4626,7 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Плавильня</t>
+          <t>Литейная</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -4652,35 +4644,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>2 Ж/руда + 2 Уголь</t>
+          <t>2 М/руда + 2 Уголь</t>
         </is>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>2 Свинец + 1 Инструмент</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>4 Железо</t>
+          <t>3 Медь</t>
         </is>
       </c>
       <c r="K80" s="9" t="inlineStr">
         <is>
-          <t>«Чугун», «Доменная печь», «Тигельная сталь»</t>
+          <t>«Латунь», «Колокола»</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr">
         <is>
-          <t>2+2(Железо)</t>
+          <t>2+2(Медь)</t>
         </is>
       </c>
       <c r="M80" s="9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4685,12 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Литейная</t>
+          <t>Лавка</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -4711,10 +4703,10 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>2 М/руда + 2 Уголь</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I81" s="9" t="inlineStr">
@@ -4724,22 +4716,22 @@
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>3 Медь</t>
+          <t>2 ТНП</t>
         </is>
       </c>
       <c r="K81" s="9" t="inlineStr">
         <is>
-          <t>«Латунь», «Колокола»</t>
+          <t>«Чеканка», «Басма»</t>
         </is>
       </c>
       <c r="L81" s="9" t="inlineStr">
         <is>
-          <t>2+2(Медь)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M81" s="9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4744,12 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Лавка</t>
+          <t>Оружейная</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -4770,7 +4762,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -4783,22 +4775,22 @@
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>2 ТНП</t>
+          <t>1 Х/о</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
         <is>
-          <t>«Чеканка», «Басма»</t>
+          <t>«Огнестрельное оружие», «Эргастерии»</t>
         </is>
       </c>
       <c r="L82" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M82" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4798,12 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>ремесло</t>
+          <t>торговля</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Оружейная</t>
+          <t>Рынок</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -4829,35 +4821,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr"/>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>доступно народам Запада и Севера</t>
         </is>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 Ткани + 1 Сахар</t>
         </is>
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>1 Х/о</t>
+          <t>+10% ЭТ, «Торговая хватка», «Ярмарки», «Скоморохи»</t>
         </is>
       </c>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>«Огнестрельное оружие», «Эргастерии»</t>
+          <t>«Торговая хватка», «Ярмарки», «Скоморохи»</t>
         </is>
       </c>
       <c r="L83" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3(Ткани)+10(Пряности)+5(Благовония)+5(Сахар) х2 (ин Ярмарка, Город &gt;= 9 размера)</t>
         </is>
       </c>
       <c r="M83" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -4870,12 +4862,12 @@
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Рынок</t>
+          <t>Базар</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -4888,35 +4880,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>доступно народам Запада и Севера</t>
+          <t>доступно народам Центра и Юга</t>
         </is>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>1 Ткани + 1 Сахар</t>
+          <t>+1 Пряности +1 Благовония</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>+10% ЭТ, «Торговая хватка», «Ярмарки», «Скоморохи»</t>
+          <t>+10% ЭТ, «Торговая хватка», «Меркантилизм», «Безистан»</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
         <is>
-          <t>«Торговая хватка», «Ярмарки», «Скоморохи»</t>
+          <t>«Торговая хватка», «Меркантилизм», «Безистан»</t>
         </is>
       </c>
       <c r="L84" s="9" t="inlineStr">
         <is>
-          <t>3(Ткани)+10(Пряности)+5(Благовония)+5(Сахар) х2 (ин Ярмарка, Город &gt;= 9 размера)</t>
+          <t>3(Ткани)+8(Мех)+6(Чай)+6(Табак)</t>
         </is>
       </c>
       <c r="M84" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4921,17 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Базар</t>
+          <t>Караван-сарай</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Пряности/Верблюды</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
@@ -4947,35 +4939,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>доступно народам Центра и Юга</t>
+          <t>не больше чем локаций с Верблюдами</t>
         </is>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>+1 Пряности +1 Благовония</t>
+          <t>1 Ткани + 1 Меха +1 Чай +1 Табак (после 1500)</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>+10% ЭТ, «Торговая хватка», «Меркантилизм», «Безистан»</t>
+          <t>+7% ЭТ, «Торговые караваны», «Фундуки», «Хан», «Охрана караванов», «Гостеприимство»</t>
         </is>
       </c>
       <c r="K85" s="9" t="inlineStr">
         <is>
-          <t>«Торговая хватка», «Меркантилизм», «Безистан»</t>
+          <t>«Торговые караваны», «Фундуки», «Хан», «Охрана караванов», «Гостеприимство»</t>
         </is>
       </c>
       <c r="L85" s="9" t="inlineStr">
         <is>
-          <t>3(Ткани)+8(Мех)+6(Чай)+6(Табак)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M85" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -4988,17 +4980,17 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Караван-сарай</t>
+          <t>Аптека</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Пряности/Верблюды</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
@@ -5006,30 +4998,30 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" s="5" t="inlineStr"/>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>не больше чем локаций с Верблюдами</t>
+          <t>не доступна странам с ВП Церковь=3</t>
         </is>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>1 Ткани + 1 Меха +1 Чай +1 Табак (после 1500)</t>
+          <t>1 Свинец</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>+7% ЭТ, «Торговые караваны», «Фундуки», «Хан», «Охрана караванов», «Гостеприимство»</t>
+          <t>1 Лекарства, -1% к шансу Эпидемии, +1% к Благочестию, «Табакокурение», «Дёготь», «Ятрохимия», «Токсикология», «Эликсиры», «Парфюмерия»</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr">
         <is>
-          <t>«Торговые караваны», «Фундуки», «Хан», «Охрана караванов», «Гостеприимство»</t>
+          <t>«Табакокурение», «Дёготь», «Ятрохимия», «Токсикология», «Эликсиры», «Парфюмерия»</t>
         </is>
       </c>
       <c r="L86" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M86" s="9" t="inlineStr">
@@ -5047,7 +5039,7 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Аптека</t>
+          <t>Бордель</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -5065,35 +5057,31 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr"/>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>не доступна странам с ВП Церковь=3</t>
+          <t>не доступен странам с ВП Церковь = 3</t>
         </is>
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
-          <t>1 Свинец</t>
+          <t>1 Алко</t>
         </is>
       </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>1 Лекарства, -1% к шансу Эпидемии, +1% к Благочестию, «Табакокурение», «Дёготь», «Ятрохимия», «Токсикология», «Эликсиры», «Парфюмерия»</t>
-        </is>
-      </c>
-      <c r="K87" s="9" t="inlineStr">
-        <is>
-          <t>«Табакокурение», «Дёготь», «Ятрохимия», «Токсикология», «Эликсиры», «Парфюмерия»</t>
-        </is>
-      </c>
+          <t>-2% к РВ в локации, +2% к шансу Эпидемии</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="n"/>
       <c r="L87" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5+1(Порт)</t>
         </is>
       </c>
       <c r="M87" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5094,12 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Бордель</t>
+          <t>Таверна</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -5124,7 +5112,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="9" t="inlineStr">
         <is>
           <t>не доступна странам с Исламом</t>
@@ -5137,22 +5125,18 @@
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>-2% к РВ в локации, +2% к шансу Эпидемии, «Секс-рабство», «Куртизанки», «Проституция»</t>
-        </is>
-      </c>
-      <c r="K88" s="9" t="inlineStr">
-        <is>
-          <t>«Секс-рабство», «Куртизанки», «Проституция»</t>
-        </is>
-      </c>
+          <t>+1 Шпион</t>
+        </is>
+      </c>
+      <c r="K88" s="9" t="n"/>
       <c r="L88" s="9" t="inlineStr">
         <is>
-          <t>5+1(Порт)</t>
+          <t>7 + 1 (Бордель)</t>
         </is>
       </c>
       <c r="M88" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -5165,17 +5149,17 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Таверна</t>
+          <t>Фактория</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Море</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
@@ -5183,30 +5167,30 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" s="5" t="inlineStr"/>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>доступно Торг. республикам</t>
         </is>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>1 Алко</t>
+          <t>1(Бордель)</t>
         </is>
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>+1 Шпион, «Пьянство», «Гостеприимство», «Трактир», «Водка»</t>
+          <t>+5% ЭТ у принимающей страны, «Колониализм»</t>
         </is>
       </c>
       <c r="K89" s="9" t="inlineStr">
         <is>
-          <t>«Пьянство», «Гостеприимство», «Трактир», «Водка»</t>
+          <t>«Колониализм»</t>
         </is>
       </c>
       <c r="L89" s="9" t="inlineStr">
         <is>
-          <t>7 + 1 (Бордель)</t>
+          <t>3 у принимающей, 1-10 у торг. республики</t>
         </is>
       </c>
       <c r="M89" s="9" t="inlineStr">
@@ -5224,17 +5208,17 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Фактория</t>
+          <t>Невольничий рынок</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Море</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
@@ -5242,35 +5226,27 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>доступно Торг. республикам</t>
-        </is>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>1(Бордель)</t>
-        </is>
-      </c>
+          <t>ВП Свобода &lt;0</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="n"/>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>+5% ЭТ у принимающей страны, «Колониализм»</t>
-        </is>
-      </c>
-      <c r="K90" s="9" t="inlineStr">
-        <is>
-          <t>«Колониализм»</t>
-        </is>
-      </c>
+          <t>2 Раба +1 (Рабы), -3 тыс.чел. убыль населения</t>
+        </is>
+      </c>
+      <c r="K90" s="9" t="n"/>
       <c r="L90" s="9" t="inlineStr">
         <is>
-          <t>3 у принимающей, 1-10 у торг. республики</t>
+          <t>1+1(Тюрьма)</t>
         </is>
       </c>
       <c r="M90" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5278,17 +5254,17 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>торговля</t>
+          <t>культура и наука</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Невольничий рынок</t>
+          <t>Ипподром</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -5301,35 +5277,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>ВП Свобода &lt;0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>1(Тюрьма)</t>
+          <t>1 Кони</t>
         </is>
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>2 Раба +1 (Рабы), -3 тыс.чел. убыль населения, «Ясырь», «Раболепие», «Мухтасибы»</t>
+          <t>-10% к РВ в локации, «Скачки»</t>
         </is>
       </c>
       <c r="K91" s="9" t="inlineStr">
         <is>
-          <t>«Ясырь», «Раболепие», «Мухтасибы»</t>
+          <t>«Скачки»</t>
         </is>
       </c>
       <c r="L91" s="9" t="inlineStr">
         <is>
-          <t>1+1(Тюрьма)</t>
+          <t>5+1(Конюшня)</t>
         </is>
       </c>
       <c r="M91" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5318,7 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Ипподром</t>
+          <t>Чайхана</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -5360,35 +5336,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>доступно народам Центра и Юга</t>
         </is>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>1 Кони</t>
+          <t>1 Чай</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>-10% к РВ в локации, «Скачки»</t>
+          <t>+1% «Кальян», «Восточные сладости», «Кофейни»</t>
         </is>
       </c>
       <c r="K92" s="9" t="inlineStr">
         <is>
-          <t>«Скачки»</t>
+          <t>«Кальян», «Восточные сладости», «Кофейни»</t>
         </is>
       </c>
       <c r="L92" s="9" t="inlineStr">
         <is>
-          <t>5+1(Конюшня)</t>
+          <t>4+1(Бани)+1(Караван-сарай)</t>
         </is>
       </c>
       <c r="M92" s="9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5377,7 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Чайхана</t>
+          <t>Театр</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -5419,35 +5395,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>доступно народам Центра и Юга</t>
+          <t>работает, если есть Книги</t>
         </is>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>1 Чай</t>
+          <t>1 Книги (если нет Богемы)</t>
         </is>
       </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>+1% «Кальян», «Восточные сладости», «Кофейни»</t>
+          <t>+3%, +1 Артист, +1 Музыкант, +1 Поэт, «Романтизм», «Комедия дель Арте», «Опера», «Клавесин»</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr">
         <is>
-          <t>«Кальян», «Восточные сладости», «Кофейни»</t>
+          <t>«Романтизм», «Комедия дель Арте», «Опера», «Клавесин»</t>
         </is>
       </c>
       <c r="L93" s="9" t="inlineStr">
         <is>
-          <t>4+1(Бани)+1(Караван-сарай)</t>
+          <t>3,5+1(Бордель)+1(Знать)</t>
         </is>
       </c>
       <c r="M93" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5436,7 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Театр</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -5478,35 +5454,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>работает, если есть Книги</t>
+          <t>доступно при Католичестве/Православии/Протестантизме и др.</t>
         </is>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>1 Книги (если нет Богемы)</t>
+          <t>1 Свинец</t>
         </is>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>+3%, +1 Артист, +1 Музыкант, +1 Поэт, «Романтизм», «Комедия дель Арте», «Опера», «Клавесин»</t>
+          <t>+1 н/о, +1 Золото (Алхимик), «Метафизика», «Химия»</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr">
         <is>
-          <t>«Романтизм», «Комедия дель Арте», «Опера», «Клавесин»</t>
+          <t>«Метафизика», «Химия»</t>
         </is>
       </c>
       <c r="L94" s="9" t="inlineStr">
         <is>
-          <t>3,5+1(Бордель)+1(Знать)</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M94" s="9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5495,7 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Библиотека</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -5537,35 +5513,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr"/>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>доступно при Католичестве/Православии/Протестантизме и др.</t>
+          <t>может быть 1 в стране</t>
         </is>
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>1 Свинец</t>
+          <t>1 Книги (если нет Учёного)</t>
         </is>
       </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>+1 н/о, +1 Золото (Алхимик), «Метафизика», «Химия»</t>
+          <t>+1 н/о, «Литература»</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
-          <t>«Метафизика», «Химия»</t>
+          <t>«Литература»</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -5578,12 +5554,12 @@
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Библиотека</t>
+          <t>Университет</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Провинция</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -5593,38 +5569,38 @@
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>все</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
+          <t>Холмы</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>может быть 1 в стране</t>
+          <t>доступно странам с Исламом</t>
         </is>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
-          <t>1 Книги (если нет Учёного)</t>
+          <t>1 Стекло</t>
         </is>
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>+1 н/о, «Литература»</t>
+          <t>+3 н/о, +1 Юрист, +1 Историк, +1 Философ, +1 Храм, +1 Госпиталь, «Романтизм», «Микроскоп»</t>
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr">
         <is>
-          <t>«Литература»</t>
+          <t>«Романтизм», «Микроскоп»</t>
         </is>
       </c>
       <c r="L96" s="9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M96" s="9" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5613,12 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Университет</t>
+          <t>Обсерватория</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -5652,28 +5628,28 @@
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>Холмы</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
+          <t>все</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>доступно странам с Исламом</t>
+          <t>работает до изучения «Книгопечатания»</t>
         </is>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>1 Стекло</t>
+          <t>1 Книги (если нет Священника/Учёного)</t>
         </is>
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>+3 н/о, +1 Юрист, +1 Историк, +1 Философ, +1 Храм, +1 Госпиталь, «Романтизм», «Микроскоп»</t>
+          <t>+2 н/о, +1 Астроном, «Астрономия», «Гороскопы»</t>
         </is>
       </c>
       <c r="K97" s="9" t="inlineStr">
         <is>
-          <t>«Романтизм», «Микроскоп»</t>
+          <t>«Астрономия», «Гороскопы»</t>
         </is>
       </c>
       <c r="L97" s="9" t="inlineStr">
@@ -5683,7 +5659,7 @@
       </c>
       <c r="M97" s="9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5672,7 @@
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Обсерватория</t>
+          <t>Медресе</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
@@ -5714,35 +5690,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr"/>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>работает до изучения «Книгопечатания»</t>
+          <t>доступно странам с Исламом</t>
         </is>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>1 Книги (если нет Священника/Учёного)</t>
+          <t>1 Бумага</t>
         </is>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>+2 н/о, +1 Астроном, «Астрономия», «Гороскопы»</t>
+          <t>+2 н/о, +1 Медик, +1 Богослов, +1 Философ, +1 Мечеть, «Мюриды», «Улемы», «Микроскоп»</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
         <is>
-          <t>«Астрономия», «Гороскопы»</t>
+          <t>«Мюриды», «Улемы», «Микроскоп»</t>
         </is>
       </c>
       <c r="L98" s="9" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5731,7 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Медресе</t>
+          <t>Скрипторий</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -5773,35 +5749,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr"/>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>доступно странам с Исламом</t>
+          <t>доступен странам с «Многоженство»</t>
         </is>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>1 Бумага</t>
+          <t>2 Бумага + 1 Инструмент</t>
         </is>
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>+2 н/о, +1 Медик, +1 Богослов, +1 Философ, +1 Мечеть, «Мюриды», «Улемы», «Микроскоп»</t>
+          <t>1 Книги, «Каллиграфия»</t>
         </is>
       </c>
       <c r="K99" s="9" t="inlineStr">
         <is>
-          <t>«Мюриды», «Улемы», «Микроскоп»</t>
+          <t>«Каллиграфия»</t>
         </is>
       </c>
       <c r="L99" s="9" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M99" s="9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -5814,12 +5790,12 @@
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Скрипторий</t>
+          <t>Типография</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Столица</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
@@ -5832,35 +5808,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>доступен странам с «Многоженство»</t>
+          <t>доступно при ВП Свобода &lt;0 и инн «Коррида»</t>
         </is>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>2 Бумага + 1 Инструмент</t>
+          <t>1 Украшения</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>1 Книги, «Каллиграфия»</t>
+          <t>2 Книги, «Пресса», «Цензура», «Газета», «Подвижные литеры»</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">
         <is>
-          <t>«Каллиграфия»</t>
+          <t>«Пресса», «Цензура», «Газета», «Подвижные литеры»</t>
         </is>
       </c>
       <c r="L100" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3+1(Университет)</t>
         </is>
       </c>
       <c r="M100" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -5873,12 +5849,12 @@
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Типография</t>
+          <t>Гарем</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Столица</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
@@ -5891,35 +5867,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>доступно при ВП Свобода &lt;0 и инн «Коррида»</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>1 Украшения</t>
+          <t>1 Х/о</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>2 Книги, «Пресса», «Цензура», «Газета», «Подвижные литеры»</t>
+          <t>+1 о/пр, +1 «жена», «Евнухи», «Наложницы»</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr">
         <is>
-          <t>«Пресса», «Цензура», «Газета», «Подвижные литеры»</t>
+          <t>«Евнухи», «Наложницы»</t>
         </is>
       </c>
       <c r="L101" s="9" t="inlineStr">
         <is>
-          <t>3+1(Университет)</t>
+          <t>-1+(-1 х ранг)</t>
         </is>
       </c>
       <c r="M101" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5908,7 @@
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Гарем</t>
+          <t>Арена</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
@@ -5950,7 +5926,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr"/>
       <c r="H102" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -5958,27 +5934,27 @@
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>1 Х/о</t>
+          <t>1 Звери</t>
         </is>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>+1 о/пр, +1 «жена», «Евнухи», «Наложницы»</t>
+          <t>+7,5% к РВ в локации, «Состязание», «Травля зверей», «Бои животных», «Коррида»</t>
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr">
         <is>
-          <t>«Евнухи», «Наложницы»</t>
+          <t>«Состязание», «Травля зверей», «Бои животных», «Коррида»</t>
         </is>
       </c>
       <c r="L102" s="9" t="inlineStr">
         <is>
-          <t>-1+(-1 х ранг)</t>
+          <t>5+1(Зверинец)</t>
         </is>
       </c>
       <c r="M102" s="9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -5991,12 +5967,12 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Арена</t>
+          <t>Зверинец</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -6009,7 +5985,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" s="5" t="inlineStr"/>
       <c r="H103" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -6017,27 +5993,23 @@
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>1 Звери</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>+7,5% к РВ в локации, «Состязание», «Травля зверей», «Бои животных», «Коррида»</t>
-        </is>
-      </c>
-      <c r="K103" s="9" t="inlineStr">
-        <is>
-          <t>«Состязание», «Травля зверей», «Бои животных», «Коррида»</t>
-        </is>
-      </c>
+          <t>-5% к РВ в локации</t>
+        </is>
+      </c>
+      <c r="K103" s="9" t="n"/>
       <c r="L103" s="9" t="inlineStr">
         <is>
-          <t>5+1(Зверинец)</t>
+          <t>(Дворец)</t>
         </is>
       </c>
       <c r="M103" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -6045,12 +6017,12 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>культура и наука</t>
+          <t>инфраструктура</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Зверинец</t>
+          <t>Дорога</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
@@ -6068,26 +6040,18 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="9" t="n"/>
+      <c r="I104" s="9" t="n"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>-5% к РВ в локации</t>
+          <t>+3% к эфф-сти Управления, +1 к макс. размеру локации</t>
         </is>
       </c>
       <c r="K104" s="9" t="n"/>
       <c r="L104" s="9" t="inlineStr">
         <is>
-          <t>(Дворец)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M104" s="9" t="inlineStr">
@@ -6105,12 +6069,12 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Дорога</t>
+          <t>Мощёная дорога</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -6123,30 +6087,30 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>1 в стране, доступна народам Запада</t>
+          <t>используемые тг&gt;=3</t>
         </is>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>1-3 Кони</t>
+          <t>1-3 Кони [зависит от числа Мощ/дорог в стране]</t>
         </is>
       </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>+3% к эфф-сти Управления, +1 к макс. размеру локации, «Ямская служба», «Торговые караваны», «Гонцы»</t>
+          <t>до +20% к эфф-сти Управления, +1 к макс. размеру локации, «Мостовая»</t>
         </is>
       </c>
       <c r="K105" s="9" t="inlineStr">
         <is>
-          <t>«Ямская служба», «Торговые караваны», «Гонцы»</t>
+          <t>«Мостовая»</t>
         </is>
       </c>
       <c r="L105" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M105" s="9" t="inlineStr">
@@ -6164,17 +6128,17 @@
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Мощёная дорога</t>
+          <t>Ирригация</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Провинция</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Жаркий/Знойный</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
@@ -6182,35 +6146,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" s="5" t="inlineStr"/>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>используемые тг&gt;=3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>2 Рабы</t>
+          <t>1 Лекарство</t>
         </is>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>до +20% к эфф-сти Управления, +1 к макс. размеру локации, «Мостовая»</t>
+          <t>х2 пр-ва Бахчи, Плантации с Хлопком и Сахаром, +2 к макс. размеру локации, «Нория»</t>
         </is>
       </c>
       <c r="K106" s="9" t="inlineStr">
         <is>
-          <t>«Мостовая»</t>
+          <t>«Нория»</t>
         </is>
       </c>
       <c r="L106" s="9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M106" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6187,7 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Ирригация</t>
+          <t>Колодец</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
@@ -6233,7 +6197,7 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>Жаркий/Знойный</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
@@ -6241,7 +6205,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -6249,17 +6213,17 @@
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>1 Лекарство</t>
+          <t>1 Ткани</t>
         </is>
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>х2 пр-ва Бахчи, Плантации с Хлопком и Сахаром, +2 к макс. размеру локации, «Нория»</t>
+          <t>+2 к макс. размеру локации, +0,5 тыс.чел. прирост населения</t>
         </is>
       </c>
       <c r="K107" s="9" t="inlineStr">
         <is>
-          <t>«Нория»</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L107" s="9" t="inlineStr">
@@ -6269,7 +6233,7 @@
       </c>
       <c r="M107" s="9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6282,12 +6246,12 @@
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Колодец</t>
+          <t>Водопровод</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
@@ -6300,7 +6264,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr"/>
       <c r="H108" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -6308,12 +6272,12 @@
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>1 Ткани</t>
+          <t>1 Золото, 1 Серебро</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>+2 к макс. размеру локации, +0,5 тыс.чел. прирост населения</t>
+          <t>+2 к макс. размеру локации, +15% к приросту населения</t>
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr">
@@ -6323,12 +6287,12 @@
       </c>
       <c r="L108" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M108" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6305,7 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Водопровод</t>
+          <t>Канализация</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
@@ -6359,7 +6323,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -6367,12 +6331,12 @@
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>1 Золото, 1 Серебро</t>
+          <t>1 Волокно</t>
         </is>
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>+2 к макс. размеру локации, +15% к приросту населения</t>
+          <t>+2 к макс. размеру локации, -5% к шансу Эпидемии</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr">
@@ -6382,12 +6346,12 @@
       </c>
       <c r="L109" s="9" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M109" s="9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -6400,12 +6364,12 @@
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Канализация</t>
+          <t>Бани</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -6418,35 +6382,27 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr"/>
       <c r="H110" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>1 Волокно</t>
-        </is>
-      </c>
+      <c r="I110" s="9" t="n"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>+2 к макс. размеру локации, -5% к шансу Эпидемии</t>
-        </is>
-      </c>
-      <c r="K110" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>+2 к макс. размеру локации, -1% к шансу Эпидемии</t>
+        </is>
+      </c>
+      <c r="K110" s="9" t="n"/>
       <c r="L110" s="9" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>1,5+1(Мыловарня)</t>
         </is>
       </c>
       <c r="M110" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6415,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Бани</t>
+          <t>Госпиталь</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
@@ -6477,7 +6433,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr"/>
       <c r="H111" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -6485,27 +6441,27 @@
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>1 Древесина</t>
+          <t>1 Лекарство</t>
         </is>
       </c>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>+2 к макс. размеру локации, -1% к шансу Эпидемии, «Хамам»</t>
+          <t>нет ивентов «Трущебы», -3% к шансу Эпидемии, уменьшение боевых потерь, «Хирургия», «Анатомия», «богадельни»</t>
         </is>
       </c>
       <c r="K111" s="9" t="inlineStr">
         <is>
-          <t>«Хамам»</t>
+          <t>«Хирургия», «Анатомия», «богадельни»</t>
         </is>
       </c>
       <c r="L111" s="9" t="inlineStr">
         <is>
-          <t>1,5+1(Мыловарня)</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M111" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6474,7 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Госпиталь</t>
+          <t>Амбар</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
@@ -6536,7 +6492,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr"/>
       <c r="H112" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -6544,27 +6500,27 @@
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
-          <t>1 Лекарство</t>
+          <t>1 Ткани</t>
         </is>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>нет ивентов «Трущебы», -3% к шансу Эпидемии, уменьшение боевых потерь, «Хирургия», «Анатомия», «богадельни»</t>
+          <t>-1-2 п/п к потребности Города, +2 к лимиту хранения, «Фортификация», «Нория», «Фундуки»</t>
         </is>
       </c>
       <c r="K112" s="9" t="inlineStr">
         <is>
-          <t>«Хирургия», «Анатомия», «богадельни»</t>
+          <t>«Фортификация», «Нория», «Фундуки»</t>
         </is>
       </c>
       <c r="L112" s="9" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M112" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -6577,12 +6533,12 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Амбар</t>
+          <t>Банк</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -6595,7 +6551,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
       <c r="H113" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -6603,27 +6559,27 @@
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>1 Ткани</t>
+          <t>1 Золото, 1 Серебро</t>
         </is>
       </c>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>-1-2 п/п к потребности Города, +2 к лимиту хранения, «Фортификация», «Нория», «Фундуки»</t>
+          <t>+1,5% х кэш (Серебро) + 3% х кэш (Золото), + к сумме внутр. займа, «депозит», «чеки», «Ломбард»</t>
         </is>
       </c>
       <c r="K113" s="9" t="inlineStr">
         <is>
-          <t>«Фортификация», «Нория», «Фундуки»</t>
+          <t>«депозит», «чеки», «Ломбард»</t>
         </is>
       </c>
       <c r="L113" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>% от кэша х2 (Евреи)</t>
         </is>
       </c>
       <c r="M113" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -6636,12 +6592,12 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Банк</t>
+          <t>Пристань</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Река/Море/Озеро</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
@@ -6654,7 +6610,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
       <c r="H114" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -6662,27 +6618,27 @@
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>1 Золото, 1 Серебро</t>
+          <t>1 Волокно</t>
         </is>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>+1,5% х кэш (Серебро) + 3% х кэш (Золото), + к сумме внутр. займа, «депозит», «чеки», «Ломбард»</t>
+          <t>2 п/п +1(Моржи) +1(Рыба) +1 ТНП</t>
         </is>
       </c>
       <c r="K114" s="9" t="inlineStr">
         <is>
-          <t>«депозит», «чеки», «Ломбард»</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L114" s="9" t="inlineStr">
         <is>
-          <t>% от кэша х2 (Евреи)</t>
+          <t>0+1(Коптильня)</t>
         </is>
       </c>
       <c r="M114" s="9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -6695,17 +6651,17 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Пристань</t>
+          <t>Гавань</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Река/Море/Озеро</t>
+          <t>Море</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>все</t>
+          <t>Жемчуг/Янтарь</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
@@ -6713,7 +6669,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr"/>
       <c r="H115" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -6721,27 +6677,27 @@
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>1 Волокно</t>
+          <t>1 Древесина</t>
         </is>
       </c>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>2 п/п +1(Моржи) +1(Рыба) +1 ТНП</t>
+          <t>1 Др/камни, -25% затрат на логистику, до +25% эфф-сть Торговли, «Топчаковые краны»</t>
         </is>
       </c>
       <c r="K115" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«Топчаковые краны»</t>
         </is>
       </c>
       <c r="L115" s="9" t="inlineStr">
         <is>
-          <t>0+1(Коптильня)</t>
+          <t>1+1(Амбар)</t>
         </is>
       </c>
       <c r="M115" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -6754,28 +6710,28 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Гавань</t>
+          <t>Порт</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
+          <t>Город</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
           <t>Море</t>
         </is>
       </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>Жемчуг/Янтарь</t>
-        </is>
-      </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
           <t>все</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr"/>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>численность Флота &gt;=2</t>
         </is>
       </c>
       <c r="I116" s="9" t="inlineStr">
@@ -6785,22 +6741,22 @@
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>1 Др/камни, -25% затрат на логистику, до +25% эфф-сть Торговли, «Топчаковые краны»</t>
+          <t>-30% к затратам на содержание Флота, +0,5 тыс.чел. прирост населения, +10 к лимиту хранения, «Торговые флотилии»</t>
         </is>
       </c>
       <c r="K116" s="9" t="inlineStr">
         <is>
-          <t>«Топчаковые краны»</t>
+          <t>«Торговые флотилии»</t>
         </is>
       </c>
       <c r="L116" s="9" t="inlineStr">
         <is>
-          <t>1+1(Амбар)</t>
+          <t>1 х Размер Города +3 (Маяк)</t>
         </is>
       </c>
       <c r="M116" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -6813,12 +6769,12 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Порт</t>
+          <t>Маяк</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Провинция/Город</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -6831,10 +6787,10 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr"/>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>численность Флота &gt;=2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I117" s="9" t="inlineStr">
@@ -6844,22 +6800,22 @@
       </c>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>-30% к затратам на содержание Флота, +0,5 тыс.чел. прирост населения, +10 к лимиту хранения, «Торговые флотилии»</t>
+          <t>+1 к дальности размещения ТОР, «Оптика», «Лоцманы»</t>
         </is>
       </c>
       <c r="K117" s="9" t="inlineStr">
         <is>
-          <t>«Торговые флотилии»</t>
+          <t>«Оптика», «Лоцманы»</t>
         </is>
       </c>
       <c r="L117" s="9" t="inlineStr">
         <is>
-          <t>1 х Размер Города +3 (Маяк)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M117" s="9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6823,12 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>инфраструктура</t>
+          <t>религия</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Маяк</t>
+          <t>Капище</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
@@ -6882,7 +6838,7 @@
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>Море</t>
+          <t>все</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr">
@@ -6890,25 +6846,25 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr"/>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>доступно странам с Язычеством</t>
         </is>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
-          <t>1 Древесина</t>
-        </is>
-      </c>
-      <c r="J118" s="9" t="inlineStr">
-        <is>
-          <t>+1 к дальности размещения ТОР, «Оптика», «Лоцманы»</t>
+          <t>1 Благовония (без 50% эфф-сть)</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>-3% к РВ в локации, +1 о/в, «Жертвоприношения»</t>
         </is>
       </c>
       <c r="K118" s="9" t="inlineStr">
         <is>
-          <t>«Оптика», «Лоцманы»</t>
+          <t>«Жертвоприношения»</t>
         </is>
       </c>
       <c r="L118" s="9" t="inlineStr">
@@ -6918,9 +6874,10 @@
       </c>
       <c r="M118" s="9" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N118" s="9" t="n"/>
     </row>
     <row r="119" ht="35.25" customHeight="1" s="6">
       <c r="A119" s="5" t="n"/>
@@ -6931,12 +6888,12 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Капище</t>
+          <t>Церковь</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Провинция/Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
@@ -6949,10 +6906,10 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="9" t="inlineStr">
         <is>
-          <t>доступно странам с Язычеством</t>
+          <t>доступно странам с Католичеством, Православием, Миафизитством, Протестантизмом, Реформаторством, Англиканством, а также с Несторианами</t>
         </is>
       </c>
       <c r="I119" s="9" t="inlineStr">
@@ -6962,85 +6919,79 @@
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>-3% к РВ в локации, +1 о/в, «Жертвоприношения»</t>
-        </is>
-      </c>
-      <c r="K119" s="9" t="inlineStr">
-        <is>
-          <t>«Жертвоприношения»</t>
-        </is>
-      </c>
+          <t>-5% к РВ в локации, +1 о/в</t>
+        </is>
+      </c>
+      <c r="K119" s="9" t="n"/>
       <c r="L119" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M119" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N119" s="9" t="n"/>
     </row>
     <row r="120" ht="57.75" customHeight="1" s="6">
-      <c r="A120" s="5" t="n"/>
-      <c r="B120" s="9" t="inlineStr">
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>религия</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>Церковь</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>Город/Провинция</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>все</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>все</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" s="9" t="inlineStr">
-        <is>
-          <t>доступно странам с Католичеством/Православием и др.</t>
-        </is>
-      </c>
-      <c r="I120" s="9" t="inlineStr">
-        <is>
-          <t>1 Благовония (без 50% эфф-сть)</t>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Храм</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Город</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr"/>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>доступно странам с Католичеством/Православием/Иудаизмом</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>1 Алко (если нет Священника)</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>-5% к РВ в локации, +1 о/в, «Простота ритуала», «Богослужение на родном языке», «Сусальное золото», «Запрет латыни»</t>
-        </is>
-      </c>
-      <c r="K120" s="9" t="inlineStr">
-        <is>
-          <t>«Простота ритуала», «Богослужение на родном языке», «Сусальное золото», «Запрет латыни»</t>
-        </is>
-      </c>
-      <c r="L120" s="9" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="M120" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N120" s="9" t="n"/>
+          <t>-10% РВ в локации, +3 о/в, «Акустика», «Простота ритуала», «Богослужение на родном языке», «Запрет латыни», «Хоровое пение», «Колокола»</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>«Акустика», «Простота ритуала», «Богослужение на родном языке», «Запрет латыни», «Хоровое пение», «Колокола»</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="12.75" customHeight="1" s="6">
       <c r="B121" s="5" t="inlineStr">
@@ -7050,12 +7001,12 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Храм</t>
+          <t>Монастырь</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -7068,10 +7019,10 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>доступно странам с Католичеством/Православием/Иудаизмом</t>
+          <t>доступно странам с Католичеством, Православием, Миафизитством</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -7081,14 +7032,10 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>-10% РВ в локации, +3 о/в, «Акустика», «Простота ритуала», «Богослужение на родном языке», «Запрет латыни», «Хоровое пение», «Колокола»</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>«Акустика», «Простота ритуала», «Богослужение на родном языке», «Запрет латыни», «Хоровое пение», «Колокола»</t>
-        </is>
-      </c>
+          <t>2 н/о +1 Монах, +1% Благочестие</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n"/>
       <c r="L121" s="5" t="inlineStr">
         <is>
           <t>-2</t>
@@ -7096,7 +7043,7 @@
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7055,7 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Монастырь</t>
+          <t>Мечеть</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -7126,25 +7073,25 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>доступно странам с Католичеством/Православием</t>
+          <t>доступно странам с Исламом и Исмаилитами</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>1 Благовоние (без 50% эфф-сть)</t>
+          <t>1 Алко (если нет Священника)</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>2 н/о +1 Монах, +1% Благочестие, «Бенефиций», «Богослужение на родном языке»</t>
+          <t>-7% к РВ в локации, +1,5 о/в, «Богослужение на родном языке», «Арабеска», «чётки», «Имамы»</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>«Бенефиций», «Богослужение на родном языке»</t>
+          <t>«Богослужение на родном языке», «Арабеска», «чётки», «Имамы»</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
@@ -7154,7 +7101,7 @@
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7113,7 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Мечеть</t>
+          <t>Святилище</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -7184,35 +7131,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr"/>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>доступно странам с Исламом и Исмаилитами</t>
+          <t>доступно странам с Иудаизмом и Зороастризмом</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>1 Алко (если нет Священника)</t>
+          <t>1 Благовоние (без 50% эфф-сть)</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>-7% к РВ в локации, +1,5 о/в, «Богослужение на родном языке», «Арабеска», «чётки», «Имамы»</t>
+          <t>-5% к РВ в локации, +1,5 о/в, «Богослужение на родном языке»</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>«Богослужение на родном языке», «Арабеска», «чётки», «Имамы»</t>
+          <t>«Богослужение на родном языке»</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7171,7 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Святилище</t>
+          <t>Мавзолей</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -7242,35 +7189,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>доступно странам с Иудаизмом и Зороастризмом</t>
+          <t>доступно странам с Суннизмом и Шиизмом</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>1 Благовоние (без 50% эфф-сть)</t>
+          <t>1 Алко (если нет Священника)</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>-5% к РВ в локации, +1,5 о/в, «Богослужение на родном языке»</t>
+          <t>5 а/в, «Гробницы»</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>«Богослужение на родном языке»</t>
+          <t>«Гробницы»</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -7282,12 +7229,12 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Мавзолей</t>
+          <t>Курган</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Провинция</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -7300,25 +7247,25 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>доступно странам с Суннизмом и Шиизмом</t>
+          <t>доступно странам с Язычеством и Тенгрианством</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>1 Алко (если нет Священника)</t>
+          <t>1 Благовоние (без 50% эфф-сть)</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>5 а/в, «Гробницы»</t>
+          <t>0,5 в/о, «Поминовение усопших»</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>«Гробницы»</t>
+          <t>«Поминовение усопших»</t>
         </is>
       </c>
       <c r="L125" s="5" t="inlineStr">
@@ -7328,24 +7275,24 @@
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12.75" customHeight="1" s="6">
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>религия</t>
+          <t>военные</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Курган</t>
+          <t>Частокол</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Провинция</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -7358,35 +7305,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr"/>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>доступно странам с Язычеством и Тенгрианством</t>
+          <t>доступно народам Центра и Юга, нужна Гончарная</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>1 Благовоние (без 50% эфф-сть)</t>
+          <t>1 Доспехи</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>0,5 в/о, «Поминовение усопших»</t>
+          <t>1 БО локации, «Засечная черта», «Городища»</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>«Поминовение усопших»</t>
+          <t>«Засечная черта», «Городища»</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7398,12 +7345,12 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Частокол</t>
+          <t>Деревянная стена</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -7416,35 +7363,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr"/>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>доступно народам Центра и Юга, нужна Гончарная</t>
+          <t>доступно народам Запада, скандинавам и литовцам</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>1 Доспехи</t>
+          <t>3 п/п</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>1 БО локации, «Засечная черта», «Городища»</t>
+          <t>3 БО локации, «Фортификация», «Городища»</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t>«Засечная черта», «Городища»</t>
+          <t>«Фортификация», «Городища»</t>
         </is>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7403,7 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Деревянная стена</t>
+          <t>Глиняная стена</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -7474,7 +7421,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr"/>
       <c r="H128" s="5" t="inlineStr">
         <is>
           <t>доступно народам Запада, скандинавам и литовцам</t>
@@ -7487,12 +7434,12 @@
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>3 БО локации, «Фортификация», «Городища»</t>
+          <t>4,5 БО локации, «Рибат», «Бойницы»</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
-          <t>«Фортификация», «Городища»</t>
+          <t>«Рибат», «Бойницы»</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
@@ -7502,7 +7449,7 @@
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7461,7 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Глиняная стена</t>
+          <t>Каменная стена</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -7532,35 +7479,27 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr"/>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>доступно народам Запада, скандинавам и литовцам</t>
-        </is>
-      </c>
-      <c r="I129" s="5" t="inlineStr">
-        <is>
-          <t>3 п/п</t>
-        </is>
-      </c>
+          <t>можно строить в условиях войны</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="n"/>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>4,5 БО локации, «Рибат», «Бойницы»</t>
-        </is>
-      </c>
-      <c r="K129" s="5" t="inlineStr">
-        <is>
-          <t>«Рибат», «Бойницы»</t>
-        </is>
-      </c>
+          <t>6 БО локации</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n"/>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -7572,12 +7511,12 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Каменная стена</t>
+          <t>Замок</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Город/Провинция</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -7590,35 +7529,35 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr"/>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>можно строить в условиях войны</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>2 Алко</t>
+          <t>1 Доспехи</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>6 БО локации, «Фортификация», «Ров», «Бойницы», «Жидкий огонь», «Бастионы»</t>
+          <t>4 БО локации +2 (Остров), «Хранители замков», «Мотт», «Донжон», «Ров»</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
         <is>
-          <t>«Фортификация», «Ров», «Бойницы», «Жидкий огонь», «Бастионы»</t>
+          <t>«Хранители замков», «Мотт», «Донжон», «Ров»</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -7630,12 +7569,12 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Замок</t>
+          <t>Ристалище</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Город/Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -7648,7 +7587,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
       <c r="H131" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -7656,27 +7595,27 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>1 Доспехи</t>
+          <t>3 п/п</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>4 БО локации +2 (Остров), «Хранители замков», «Мотт», «Донжон», «Ров»</t>
+          <t>+0,5 к силе ТК, +0,5 в/о, решение «Провести рыц. турнир»</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>«Хранители замков», «Мотт», «Донжон», «Ров»</t>
+          <t>«Провести рыц. турнир»</t>
         </is>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -7688,12 +7627,12 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Ристалище</t>
+          <t>Лагерь</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Город</t>
+          <t>Провинция</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -7706,7 +7645,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
       <c r="H132" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -7714,27 +7653,22 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>3 п/п</t>
+          <t>2 Алко</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>+0,5 к силе ТК, +0,5 в/о, решение «Провести рыц. турнир»</t>
-        </is>
-      </c>
-      <c r="K132" s="5" t="inlineStr">
-        <is>
-          <t>«Провести рыц. турнир»</t>
+          <t>2 БО локации, 1 в/о, +3 к снабжению</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -7746,12 +7680,12 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Лагерь</t>
+          <t>Казарма</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Провинция</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -7764,7 +7698,7 @@
           <t>все</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr"/>
       <c r="H133" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -7772,17 +7706,17 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>2 Алко</t>
+          <t>1 Доспехи</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>2 БО локации, 1 в/о, +3 к снабжению</t>
+          <t>-100% к снижению затрат на содержание Армии, 2 в/о</t>
         </is>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M133" s="5" t="inlineStr">
@@ -7791,59 +7725,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="12.75" customHeight="1" s="6">
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>военные</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>Казарма</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>Город</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>все</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>все</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr">
-        <is>
-          <t>1 Доспехи</t>
-        </is>
-      </c>
-      <c r="J134" s="5" t="inlineStr">
-        <is>
-          <t>-100% к снижению затрат на содержание Армии, 2 в/о</t>
-        </is>
-      </c>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M134" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
+    <row r="134" ht="12.75" customHeight="1" s="6"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/dev/buildings.xlsx
+++ b/dev/buildings.xlsx
@@ -3006,11 +3006,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>1 Древесина, 1 Сахар</t>
-        </is>
-      </c>
+      <c r="I52" s="9" t="n"/>
       <c r="J52" s="9" t="inlineStr">
         <is>
           <t>0 Краски +2 (Краситель)</t>
@@ -3531,7 +3527,7 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>3 Волокно + 1 Краски</t>
+          <t>2 Волокно</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
@@ -7032,7 +7028,7 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>2 н/о +1 Монах, +1% Благочестие</t>
+          <t>2 кт/о + 1 (Монах), +1% Благочестие</t>
         </is>
       </c>
       <c r="K121" s="5" t="n"/>

--- a/dev/buildings.xlsx
+++ b/dev/buildings.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="633">
   <si>
     <t xml:space="preserve">Группа</t>
   </si>
@@ -61,6 +61,12 @@
     <t xml:space="preserve">Цена</t>
   </si>
   <si>
+    <t xml:space="preserve">Примечания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ресурсы на постройку</t>
+  </si>
+  <si>
     <t xml:space="preserve">Поле</t>
   </si>
   <si>
@@ -160,6 +166,9 @@
     <t xml:space="preserve">30</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Огород</t>
   </si>
   <si>
@@ -175,6 +184,9 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Свинарник</t>
   </si>
   <si>
@@ -208,6 +220,9 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Бахча</t>
   </si>
   <si>
@@ -274,6 +289,9 @@
     <t xml:space="preserve">«Водяное колесо», «Ветряные мельницы», «Механизация труда»</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×3, инстр×1, ткани×1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Маслобойня</t>
   </si>
   <si>
@@ -286,6 +304,9 @@
     <t xml:space="preserve">20</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Конюшня</t>
   </si>
   <si>
@@ -358,6 +379,9 @@
     <t xml:space="preserve">Сахарная мельница, Террасное земледелие</t>
   </si>
   <si>
+    <t xml:space="preserve">+1 к пр-ву только на о.Кипр (21-й ход)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Хлопок</t>
   </si>
   <si>
@@ -376,6 +400,9 @@
     <t xml:space="preserve">26</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Шёлк</t>
   </si>
   <si>
@@ -469,6 +496,9 @@
     <t xml:space="preserve">50</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Таможня</t>
   </si>
   <si>
@@ -523,6 +553,9 @@
     <t xml:space="preserve">100</t>
   </si>
   <si>
+    <t xml:space="preserve">стекло×3, мрамор×10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Рудник</t>
   </si>
   <si>
@@ -541,6 +574,9 @@
     <t xml:space="preserve">«Маркшейдеры», «Амальгамация», «Горное дело», «Тяга», «Водяные насосы»</t>
   </si>
   <si>
+    <t xml:space="preserve">1 + 1 (Дорога)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Серебро</t>
   </si>
   <si>
@@ -625,6 +661,9 @@
     <t xml:space="preserve">«Угольная печь», «Чугун»</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Смолокурня</t>
   </si>
   <si>
@@ -769,6 +808,9 @@
     <t xml:space="preserve">1+2(Сахар*)</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×3, камень×3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Пивоварня</t>
   </si>
   <si>
@@ -802,6 +844,9 @@
     <t xml:space="preserve">«Водка», «Ракия»</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×5, медь×3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Свеч/артель</t>
   </si>
   <si>
@@ -823,6 +868,9 @@
     <t xml:space="preserve">«Гербовая бумага», «Водяное колесо», «Механизация труда», «Гильдии»</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Перг/артель</t>
   </si>
   <si>
@@ -859,6 +907,9 @@
     <t xml:space="preserve">«Сухой док», «Клинкер», «Адмиралтейство», «Ветряная пилорама»</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ткац/артель</t>
   </si>
   <si>
@@ -880,6 +931,9 @@
     <t xml:space="preserve">«Экономика», «Разделение труда», «Цеховые привилегии»</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×5, камень×5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Сукновальня</t>
   </si>
   <si>
@@ -1069,6 +1123,9 @@
     <t xml:space="preserve">«Горн», «Вагранка», «Сыродутная печь», «Булатная сталь», «Подкова»</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×3, камень×2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Плавильня</t>
   </si>
   <si>
@@ -1120,6 +1177,9 @@
     <t xml:space="preserve">«Огнестрельное оружие», «Эргастерии»</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×4, камень×2</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 Свинец + 1 Инструмент</t>
   </si>
   <si>
@@ -1147,6 +1207,9 @@
     <t xml:space="preserve">3(Ткани*)+10(Пряности*)+5(Благовония*)+5(Сахар*) х2 (инн Ярмарка, наличие в стране Города 9+ размера)</t>
   </si>
   <si>
+    <t xml:space="preserve">+1 ТНП и +3 п/п к потребности (24-й ход)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Базар</t>
   </si>
   <si>
@@ -1267,6 +1330,9 @@
     <t xml:space="preserve">5+1(Конюшня)</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Чайхана</t>
   </si>
   <si>
@@ -1300,6 +1366,9 @@
     <t xml:space="preserve">80</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×7, мрамор×5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Лаборатория</t>
   </si>
   <si>
@@ -1342,6 +1411,9 @@
     <t xml:space="preserve">90</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×10, стекло×3, мрамор×3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Обсерватория</t>
   </si>
   <si>
@@ -1357,6 +1429,9 @@
     <t xml:space="preserve">«Астрономия», «Гороскопы»</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Медресе</t>
   </si>
   <si>
@@ -1447,6 +1522,9 @@
     <t xml:space="preserve">3+2(Дворец)</t>
   </si>
   <si>
+    <t xml:space="preserve">железо×3</t>
+  </si>
+  <si>
     <t xml:space="preserve">инфраструктура</t>
   </si>
   <si>
@@ -1495,12 +1573,18 @@
     <t xml:space="preserve">+2 к макс. размеру локации, +15% к приросту населения в Городе</t>
   </si>
   <si>
+    <t xml:space="preserve">свинец×5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Канализация</t>
   </si>
   <si>
     <t xml:space="preserve">+2 к макс. размеру локации, -5% к шансу Эпидемии в Городе</t>
   </si>
   <si>
+    <t xml:space="preserve">медь×5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Бани</t>
   </si>
   <si>
@@ -1534,6 +1618,12 @@
     <t xml:space="preserve">«Фортификация», «Нория», «Фундуки»</t>
   </si>
   <si>
+    <t xml:space="preserve">26 мая 2026 Мельхиор выпустил патч, изменена потребность Амбаров с Тканей на ТНП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">древ×2, камень×2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Банк</t>
   </si>
   <si>
@@ -1612,6 +1702,9 @@
     <t xml:space="preserve">«Оптика», «Лоцманы»</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×7, стекло×1</t>
+  </si>
+  <si>
     <t xml:space="preserve">религия</t>
   </si>
   <si>
@@ -1648,21 +1741,27 @@
     <t xml:space="preserve">доступно странам с Католичеством/Православием/Миафизитством/Иудаизмом</t>
   </si>
   <si>
+    <t xml:space="preserve">-10% к РВ в локации, +3 о/в</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Акустика», «Простота ритуала», «Богослужение на родном языке», «Запрет латыни», «Хоровое пение», «Колокола»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−10% к стоимости стабильности; не суммируется (30-й ход)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">стекло×2, мрамор×10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Монастырь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">доступно странам с Католичеством, Православием, Миафизитством</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 Алко (если нет Священника)</t>
   </si>
   <si>
-    <t xml:space="preserve">-10% к РВ в локации, +3 о/в</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Акустика», «Простота ритуала», «Богослужение на родном языке», «Запрет латыни», «Хоровое пение», «Колокола»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Монастырь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">доступно странам с Католичеством, Православием, Миафизитством</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 кт/о + 1 (Монах), +1% Благочестие в ход</t>
   </si>
   <si>
@@ -1705,6 +1804,9 @@
     <t xml:space="preserve">«Гробницы»</t>
   </si>
   <si>
+    <t xml:space="preserve">мрамор×15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Курган</t>
   </si>
   <si>
@@ -1732,6 +1834,9 @@
     <t xml:space="preserve">-0.5</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Дер/стена</t>
   </si>
   <si>
@@ -1741,6 +1846,9 @@
     <t xml:space="preserve">«Фортификация», «Городища»</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Глин/стена</t>
   </si>
   <si>
@@ -1762,6 +1870,9 @@
     <t xml:space="preserve">«Фортификация», «Ров», «Бойницы», «Жидкий огонь», «Бастионы»</t>
   </si>
   <si>
+    <t xml:space="preserve">камень×20</t>
+  </si>
+  <si>
     <t xml:space="preserve">Замок</t>
   </si>
   <si>
@@ -1774,6 +1885,9 @@
     <t xml:space="preserve">Трад. «Хранители замков», «Мотт», «Донжон», «Ров»</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×5, камень×15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ристалище</t>
   </si>
   <si>
@@ -1783,6 +1897,9 @@
     <t xml:space="preserve">+0,5 к силе ТК, +0,5 в/о, открытие решения «Провести рыц. турнир»</t>
   </si>
   <si>
+    <t xml:space="preserve">древ×7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Лагерь</t>
   </si>
   <si>
@@ -1790,6 +1907,9 @@
   </si>
   <si>
     <t xml:space="preserve">2 БО локации, 1 в/о, +3 к снабжению</t>
+  </si>
+  <si>
+    <t xml:space="preserve">древ×4, ткани×2</t>
   </si>
   <si>
     <t xml:space="preserve">Казарма</t>
@@ -1892,25 +2012,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2036,7 +2160,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N138"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.75"/>
@@ -2082,580 +2206,607 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
       <c r="B9" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="M9" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
       <c r="B10" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
       <c r="B12" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1"/>
       <c r="B16" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>0</v>
@@ -2666,35 +2817,35 @@
     </row>
     <row r="18" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>0</v>
@@ -2705,35 +2856,35 @@
     </row>
     <row r="19" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>0</v>
@@ -2744,35 +2895,35 @@
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>0</v>
@@ -2780,38 +2931,41 @@
       <c r="M20" s="1" t="n">
         <v>35</v>
       </c>
+      <c r="N20" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>0</v>
@@ -2822,16 +2976,16 @@
     </row>
     <row r="22" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -2841,67 +2995,70 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="4" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -2909,557 +3066,629 @@
     <row r="25" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1"/>
       <c r="B25" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1"/>
       <c r="B26" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1"/>
       <c r="B27" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1"/>
       <c r="B28" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>148</v>
+        <v>157</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1"/>
       <c r="B29" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1"/>
       <c r="B30" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1"/>
       <c r="B31" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L32" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="M32" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L33" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="M33" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L34" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="M34" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L35" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="M35" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L36" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="M36" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L37" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="M37" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -3467,3543 +3696,3822 @@
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1"/>
       <c r="B42" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1"/>
       <c r="B43" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1"/>
       <c r="B44" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1"/>
       <c r="B47" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1"/>
       <c r="B48" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1"/>
       <c r="B53" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>240</v>
+        <v>253</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1"/>
       <c r="B54" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1"/>
       <c r="B55" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1"/>
       <c r="B56" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1"/>
       <c r="B57" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1"/>
       <c r="B58" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1"/>
       <c r="B59" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1"/>
       <c r="B60" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1"/>
       <c r="B61" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1"/>
       <c r="B62" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>148</v>
+        <v>157</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1"/>
       <c r="B63" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>240</v>
+        <v>253</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1"/>
       <c r="B64" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>50</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1"/>
       <c r="B65" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1"/>
       <c r="B66" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1"/>
       <c r="B67" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1"/>
       <c r="B68" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1"/>
       <c r="B69" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F69" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="M69" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G69" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K69" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="L69" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>22</v>
+      <c r="O69" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1"/>
       <c r="B70" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1"/>
       <c r="B71" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1"/>
       <c r="B72" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1"/>
       <c r="B73" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1"/>
       <c r="B74" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M74" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1"/>
       <c r="B75" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="4" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1"/>
       <c r="B76" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1"/>
       <c r="B77" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>336</v>
+        <v>354</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1"/>
       <c r="B78" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M78" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1"/>
       <c r="B79" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M79" s="4" t="s">
-        <v>345</v>
+        <v>363</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1"/>
       <c r="B80" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M80" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1"/>
       <c r="B81" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="M81" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1"/>
       <c r="B82" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>160</v>
+        <v>170</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1"/>
       <c r="B83" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H84" s="4"/>
       <c r="I84" s="4" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1"/>
       <c r="B86" s="4" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1"/>
       <c r="B87" s="4" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="M87" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1"/>
       <c r="B88" s="4" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="4" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="4" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1"/>
       <c r="B90" s="4" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="I90" s="4"/>
       <c r="J90" s="4" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1"/>
       <c r="B91" s="4" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="M91" s="4" t="n">
         <v>10</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1"/>
       <c r="B92" s="4" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="I92" s="4"/>
       <c r="J92" s="4" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1"/>
       <c r="B93" s="4" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="I93" s="4"/>
       <c r="J93" s="4" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="M93" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1"/>
       <c r="B94" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H94" s="4"/>
       <c r="I94" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>160</v>
+        <v>170</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1"/>
       <c r="B95" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="M95" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1"/>
       <c r="B96" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H96" s="4"/>
       <c r="I96" s="4" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="M96" s="4" t="s">
-        <v>425</v>
+        <v>447</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1"/>
       <c r="B97" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H97" s="4"/>
       <c r="I97" s="4" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M97" s="4" t="s">
-        <v>429</v>
+        <v>452</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1"/>
       <c r="B98" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="I98" s="4"/>
       <c r="J98" s="4" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M98" s="4" t="s">
-        <v>433</v>
+        <v>456</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1"/>
       <c r="B99" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="M99" s="4" t="s">
-        <v>439</v>
+        <v>462</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1"/>
       <c r="B100" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="M100" s="4" t="s">
-        <v>166</v>
+        <v>176</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1"/>
       <c r="B101" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M101" s="4" t="s">
-        <v>450</v>
+        <v>475</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1"/>
       <c r="B102" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M102" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1"/>
       <c r="B103" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H103" s="4"/>
       <c r="I103" s="4" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1"/>
       <c r="B104" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="M104" s="4" t="s">
-        <v>465</v>
+        <v>490</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1"/>
       <c r="B105" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="M105" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1"/>
       <c r="B106" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H106" s="4"/>
       <c r="I106" s="4" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="K106" s="4"/>
       <c r="L106" s="4" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="M106" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1"/>
       <c r="B107" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
       <c r="J107" s="4" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M107" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1"/>
       <c r="B108" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H108" s="4"/>
       <c r="I108" s="4" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M108" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1"/>
       <c r="B109" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H109" s="4"/>
       <c r="I109" s="4" t="s">
-        <v>484</v>
+        <v>510</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>486</v>
+        <v>512</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M109" s="4" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1"/>
       <c r="B110" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
       <c r="J110" s="4" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="K110" s="4"/>
       <c r="L110" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1"/>
       <c r="B111" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
       <c r="J111" s="4" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="K111" s="4"/>
       <c r="L111" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M111" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1"/>
       <c r="B112" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
       <c r="J112" s="4" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="K112" s="4"/>
       <c r="L112" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1"/>
       <c r="B113" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>493</v>
+        <v>521</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
       <c r="J113" s="4" t="s">
-        <v>494</v>
+        <v>522</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="M113" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1"/>
       <c r="B114" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" s="4" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>499</v>
+        <v>527</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M114" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1"/>
       <c r="B115" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H115" s="4"/>
       <c r="I115" s="4" t="s">
-        <v>280</v>
+        <v>347</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>502</v>
+        <v>530</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>503</v>
+        <v>531</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M115" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1"/>
       <c r="B116" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>505</v>
+        <v>535</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>508</v>
+        <v>538</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>509</v>
+        <v>539</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>511</v>
+        <v>541</v>
       </c>
       <c r="H117" s="4"/>
       <c r="I117" s="4" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>513</v>
+        <v>543</v>
       </c>
       <c r="K117" s="4"/>
       <c r="L117" s="4" t="s">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="M117" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="H118" s="4"/>
       <c r="I118" s="4" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="K118" s="4"/>
       <c r="L118" s="4" t="s">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="M118" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1"/>
       <c r="B119" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>517</v>
+        <v>547</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="I119" s="4"/>
       <c r="J119" s="4" t="s">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="M119" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1"/>
       <c r="B120" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>522</v>
+        <v>552</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="I120" s="4"/>
       <c r="J120" s="4" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="M120" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1"/>
       <c r="B121" s="4" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="H121" s="4"/>
       <c r="I121" s="4" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M121" s="4" t="n">
         <v>25</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1"/>
       <c r="B122" s="4" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>532</v>
+        <v>563</v>
       </c>
       <c r="I122" s="4"/>
       <c r="J122" s="1" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M122" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N122" s="4"/>
+      <c r="O122" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1"/>
       <c r="B123" s="4" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>535</v>
+        <v>566</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M123" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N123" s="4"/>
+      <c r="O123" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B124" s="1" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>541</v>
+        <v>572</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>148</v>
+        <v>157</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="O124" s="1" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B125" s="1" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>547</v>
+        <v>580</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>548</v>
+        <v>581</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>336</v>
+        <v>354</v>
+      </c>
+      <c r="O125" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B126" s="1" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>549</v>
+        <v>582</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>550</v>
+        <v>583</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>551</v>
+        <v>584</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O126" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B127" s="1" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>553</v>
+        <v>586</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>554</v>
+        <v>587</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>555</v>
+        <v>588</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>556</v>
+        <v>589</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O127" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B128" s="1" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>557</v>
+        <v>590</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>559</v>
+        <v>592</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>560</v>
+        <v>593</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
+      </c>
+      <c r="O128" s="1" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B129" s="1" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>561</v>
+        <v>595</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>562</v>
+        <v>596</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>563</v>
+        <v>597</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>564</v>
+        <v>598</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B130" s="1" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>566</v>
+        <v>600</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H130" s="1"/>
       <c r="J130" s="1" t="s">
-        <v>567</v>
+        <v>601</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>568</v>
+        <v>602</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>569</v>
+        <v>603</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="O130" s="1" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B131" s="1" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>570</v>
+        <v>605</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H131" s="1"/>
       <c r="J131" s="1" t="s">
-        <v>571</v>
+        <v>606</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>572</v>
+        <v>607</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="O131" s="1" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B132" s="1" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>573</v>
+        <v>609</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>574</v>
+        <v>610</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>575</v>
+        <v>611</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>576</v>
+        <v>612</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O132" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B133" s="1" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>577</v>
+        <v>613</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H133" s="1"/>
       <c r="J133" s="1" t="s">
-        <v>578</v>
+        <v>614</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>579</v>
+        <v>615</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>148</v>
+        <v>157</v>
+      </c>
+      <c r="O133" s="5" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B134" s="1" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>580</v>
+        <v>617</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
+      </c>
+      <c r="O134" s="1" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B135" s="1" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>584</v>
+        <v>622</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>585</v>
+        <v>623</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="K135" s="1"/>
       <c r="L135" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="O135" s="1" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B136" s="1" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>587</v>
+        <v>626</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>588</v>
+        <v>627</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B137" s="1" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1" t="s">
-        <v>591</v>
+        <v>631</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>592</v>
+        <v>632</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="O137" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7012,8 +7520,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12 &amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12 Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>